--- a/data/trans_camb/P1_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,58</t>
+          <t>-1,17; 7,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 19,2</t>
+          <t>8,52; 18,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 13,95</t>
+          <t>4,85; 14,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 9,44</t>
+          <t>-1,27; 8,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 10,39</t>
+          <t>-0,42; 10,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,58</t>
+          <t>2,86; 11,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 6,55</t>
+          <t>0,42; 6,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 13,72</t>
+          <t>6,44; 13,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 11,72</t>
+          <t>5,35; 11,4</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 125,38</t>
+          <t>-11,5; 119,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,54; 313,21</t>
+          <t>90,25; 319,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,84; 231,41</t>
+          <t>46,02; 237,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 142,17</t>
+          <t>-12,55; 125,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 154,4</t>
+          <t>-4,66; 137,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,22; 166,7</t>
+          <t>21,9; 169,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 93,26</t>
+          <t>2,26; 97,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,8; 192,32</t>
+          <t>63,87; 197,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,95; 165,42</t>
+          <t>53,7; 165,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 0,98</t>
+          <t>-8,41; 0,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,5</t>
+          <t>-7,66; 2,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 11,43</t>
+          <t>0,57; 11,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,6</t>
+          <t>-3,84; 4,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 10,2</t>
+          <t>1,05; 10,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 10,63</t>
+          <t>2,55; 10,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 1,71</t>
+          <t>-4,79; 1,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 4,63</t>
+          <t>-1,98; 4,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 10,27</t>
+          <t>3,15; 9,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-55,98; 10,7</t>
+          <t>-53,54; 13,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 26,36</t>
+          <t>-50,0; 25,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 123,98</t>
+          <t>4,09; 122,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 89,37</t>
+          <t>-41,08; 78,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 180,29</t>
+          <t>8,94; 178,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,34; 185,85</t>
+          <t>23,43; 189,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,65; 21,76</t>
+          <t>-42,05; 18,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 53,42</t>
+          <t>-16,79; 56,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,83; 132,96</t>
+          <t>28,38; 118,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,82</t>
+          <t>-0,62; 5,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 8,57</t>
+          <t>1,81; 8,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 14,36</t>
+          <t>-2,64; 14,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 9,91</t>
+          <t>-1,0; 9,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 18,18</t>
+          <t>2,89; 17,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 20,27</t>
+          <t>8,38; 20,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,13</t>
+          <t>0,47; 5,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,58</t>
+          <t>3,48; 9,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 14,77</t>
+          <t>0,06; 14,58</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 137,59</t>
+          <t>-10,89; 127,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,16; 199,31</t>
+          <t>22,67; 197,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 273,8</t>
+          <t>-35,41; 289,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 264,31</t>
+          <t>-19,07; 245,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,88; 456,95</t>
+          <t>25,21; 437,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,43; 556,62</t>
+          <t>79,71; 595,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,45; 130,76</t>
+          <t>4,18; 131,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,78; 207,68</t>
+          <t>47,35; 203,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 276,26</t>
+          <t>1,56; 267,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 4,27</t>
+          <t>-0,23; 4,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,17</t>
+          <t>1,63; 6,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,67; 15,43</t>
+          <t>9,61; 15,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,85</t>
+          <t>-4,39; 0,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 8,76</t>
+          <t>2,49; 8,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 8,59</t>
+          <t>-2,52; 8,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,19</t>
+          <t>-1,15; 2,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,56</t>
+          <t>2,77; 6,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 11,14</t>
+          <t>3,73; 11,19</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 73,16</t>
+          <t>-3,96; 73,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,91; 107,1</t>
+          <t>20,53; 113,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>123,81; 281,77</t>
+          <t>119,31; 271,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 14,31</t>
+          <t>-52,02; 12,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,63; 146,47</t>
+          <t>27,24; 149,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 129,87</t>
+          <t>-25,2; 127,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 37,47</t>
+          <t>-15,27; 37,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,86; 107,53</t>
+          <t>35,19; 108,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58,81; 175,76</t>
+          <t>56,54; 178,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 1,95</t>
+          <t>-6,61; 1,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 9,25</t>
+          <t>0,6; 9,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,19; 17,84</t>
+          <t>7,66; 17,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 5,19</t>
+          <t>-1,28; 5,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 6,61</t>
+          <t>-0,47; 6,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,75; 13,92</t>
+          <t>4,96; 14,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,16</t>
+          <t>-1,97; 2,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,73</t>
+          <t>1,45; 6,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,13; 14,17</t>
+          <t>7,16; 14,38</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,75; 25,04</t>
+          <t>-51,47; 24,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,26; 121,07</t>
+          <t>2,47; 123,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53,85; 233,87</t>
+          <t>60,17; 227,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 79,49</t>
+          <t>-13,54; 78,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 99,39</t>
+          <t>-5,54; 98,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,06; 205,69</t>
+          <t>54,03; 222,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 41,29</t>
+          <t>-18,5; 38,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11,37; 89,26</t>
+          <t>13,48; 87,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>70,34; 187,89</t>
+          <t>72,97; 191,17</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 3,4</t>
+          <t>-2,27; 3,14</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,89</t>
+          <t>2,44; 9,94</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 12,76</t>
+          <t>-1,06; 10,35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,55</t>
+          <t>-0,84; 4,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,58</t>
+          <t>0,71; 6,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,95; 13,04</t>
+          <t>7,06; 13,07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,65</t>
+          <t>-0,58; 3,87</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,58</t>
+          <t>1,25; 6,38</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,38; 10,67</t>
+          <t>5,32; 10,61</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-66,76; 325,81</t>
+          <t>-62,64; 293,01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>39,6; 753,64</t>
+          <t>46,78; 795,48</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-46,14; 870,54</t>
+          <t>-52,43; 700,15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 49,89</t>
+          <t>-7,71; 48,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6,48; 70,93</t>
+          <t>6,33; 67,14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,16; 142,94</t>
+          <t>61,9; 143,79</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 44,76</t>
+          <t>-5,54; 48,12</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>16,07; 83,88</t>
+          <t>12,5; 78,93</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53,17; 137,07</t>
+          <t>53,52; 133,51</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,4</t>
+          <t>-0,31; 2,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,7</t>
+          <t>3,84; 6,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,99; 11,64</t>
+          <t>5,99; 11,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,58</t>
+          <t>-0,25; 2,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,98</t>
+          <t>2,94; 6,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,5</t>
+          <t>4,77; 9,64</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,06</t>
+          <t>0,15; 2,17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,89</t>
+          <t>3,81; 6,0</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,16</t>
+          <t>6,28; 10,05</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 35,71</t>
+          <t>-3,52; 36,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>46,44; 100,06</t>
+          <t>48,82; 100,89</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>80,99; 172,44</t>
+          <t>80,53; 173,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 32,21</t>
+          <t>-2,93; 32,74</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>31,99; 73,75</t>
+          <t>30,79; 73,38</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>48,68; 116,92</t>
+          <t>53,9; 117,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,08; 27,54</t>
+          <t>1,88; 29,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>44,27; 78,43</t>
+          <t>44,39; 80,03</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>79,22; 133,18</t>
+          <t>74,6; 132,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,39</t>
+          <t>9,33</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,29</t>
+          <t>7,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,51</t>
+          <t>8,68</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 7,47</t>
+          <t>-0,48; 7,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 18,47</t>
+          <t>8,6; 18,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 14,13</t>
+          <t>4,97; 13,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 8,8</t>
+          <t>-1,47; 9,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 10,06</t>
+          <t>0,03; 10,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 11,33</t>
+          <t>3,39; 11,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,97</t>
+          <t>-0,02; 6,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 13,58</t>
+          <t>6,29; 13,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 11,4</t>
+          <t>5,73; 11,71</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118,47%</t>
+          <t>117,74%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100,49%</t>
+          <t>102,57%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 119,52</t>
+          <t>-4,21; 130,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,25; 319,66</t>
+          <t>89,87; 312,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,02; 237,35</t>
+          <t>48,39; 219,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 125,54</t>
+          <t>-13,13; 123,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 137,75</t>
+          <t>-1,92; 146,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,9; 169,5</t>
+          <t>26,35; 184,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 97,89</t>
+          <t>-0,52; 95,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>63,87; 197,53</t>
+          <t>60,64; 193,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,7; 165,72</t>
+          <t>57,8; 172,19</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,24</t>
+          <t>6,08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>6,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 0,98</t>
+          <t>-8,38; 1,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 2,43</t>
+          <t>-7,74; 2,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 11,18</t>
+          <t>0,57; 11,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 4,32</t>
+          <t>-3,64; 4,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,35</t>
+          <t>0,75; 9,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,23</t>
+          <t>3,07; 11,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,46</t>
+          <t>-4,66; 1,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,65</t>
+          <t>-1,92; 4,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 9,65</t>
+          <t>3,31; 9,95</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 13,27</t>
+          <t>-55,6; 17,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,0; 25,59</t>
+          <t>-50,78; 25,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 122,63</t>
+          <t>2,5; 118,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 78,08</t>
+          <t>-40,2; 84,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 178,72</t>
+          <t>6,9; 176,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,43; 189,32</t>
+          <t>27,62; 218,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 18,37</t>
+          <t>-39,66; 18,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 56,95</t>
+          <t>-16,44; 58,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,38; 118,36</t>
+          <t>26,9; 123,66</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,37</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>14,28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,99</t>
+          <t>13,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,6</t>
+          <t>-0,98; 5,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,59</t>
+          <t>1,72; 8,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 14,74</t>
+          <t>8,52; 16,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 9,73</t>
+          <t>-0,66; 9,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 17,77</t>
+          <t>2,71; 17,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,38; 20,62</t>
+          <t>8,19; 19,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,89</t>
+          <t>0,52; 5,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 9,56</t>
+          <t>3,33; 9,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 14,58</t>
+          <t>9,89; 16,72</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113,2%</t>
+          <t>220,89%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>225,4%</t>
+          <t>220,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>137,0%</t>
+          <t>222,97%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 127,58</t>
+          <t>-14,14; 139,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,67; 197,02</t>
+          <t>18,65; 192,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 289,38</t>
+          <t>115,58; 393,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 245,76</t>
+          <t>-9,98; 289,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,21; 437,52</t>
+          <t>24,09; 465,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79,71; 595,97</t>
+          <t>72,6; 556,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,18; 131,23</t>
+          <t>5,32; 122,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,35; 203,61</t>
+          <t>46,24; 200,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 267,45</t>
+          <t>135,34; 360,61</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,4</t>
+          <t>12,75</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,34</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,55</t>
+          <t>10,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,11</t>
+          <t>-0,13; 4,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,27</t>
+          <t>1,48; 6,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,61; 15,42</t>
+          <t>9,74; 15,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,68</t>
+          <t>-4,42; 0,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,81</t>
+          <t>2,4; 8,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 8,44</t>
+          <t>4,49; 9,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,22</t>
+          <t>-1,2; 2,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,53</t>
+          <t>2,91; 6,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 11,19</t>
+          <t>8,51; 12,47</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>185,24%</t>
+          <t>190,4%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>124,21%</t>
+          <t>150,31%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 73,04</t>
+          <t>-2,03; 75,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,53; 113,04</t>
+          <t>18,0; 109,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119,31; 271,88</t>
+          <t>127,81; 277,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,02; 12,76</t>
+          <t>-52,86; 16,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,24; 149,68</t>
+          <t>28,09; 145,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 127,48</t>
+          <t>48,42; 174,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 37,38</t>
+          <t>-15,62; 34,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,19; 108,26</t>
+          <t>37,52; 107,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>56,54; 178,74</t>
+          <t>108,44; 207,42</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12,74</t>
+          <t>14,69</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,35</t>
+          <t>11,93</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>13,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 1,68</t>
+          <t>-6,48; 1,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,6; 9,34</t>
+          <t>-0,06; 9,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,66; 17,74</t>
+          <t>9,32; 19,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 5,23</t>
+          <t>-1,09; 5,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 6,69</t>
+          <t>-0,42; 6,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,96; 14,23</t>
+          <t>8,75; 14,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 2,92</t>
+          <t>-2,13; 3,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,62</t>
+          <t>1,4; 6,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,16; 14,38</t>
+          <t>10,23; 15,89</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125,84%</t>
+          <t>145,1%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>124,11%</t>
+          <t>143,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>123,9%</t>
+          <t>145,22%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,47; 24,79</t>
+          <t>-50,34; 28,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,47; 123,74</t>
+          <t>-1,57; 118,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60,17; 227,51</t>
+          <t>70,78; 258,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 78,49</t>
+          <t>-10,58; 85,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 98,78</t>
+          <t>-4,52; 100,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,03; 222,16</t>
+          <t>82,03; 231,57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 38,82</t>
+          <t>-20,53; 46,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13,48; 87,29</t>
+          <t>14,31; 92,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>72,97; 191,17</t>
+          <t>95,56; 222,03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,1</t>
+          <t>9,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,92</t>
+          <t>7,69</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 3,14</t>
+          <t>-2,34; 3,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,94</t>
+          <t>2,53; 9,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 10,35</t>
+          <t>-1,17; 6,75</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,6</t>
+          <t>-0,88; 4,36</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,3</t>
+          <t>0,56; 6,36</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,06; 13,07</t>
+          <t>7,05; 12,68</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,87</t>
+          <t>-0,78; 3,76</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,38</t>
+          <t>1,72; 6,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,32; 10,61</t>
+          <t>5,28; 10,14</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>108,75%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-62,64; 293,01</t>
+          <t>-63,81; 261,26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>46,78; 795,48</t>
+          <t>50,76; 768,5</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,43; 700,15</t>
+          <t>-44,99; 520,26</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 48,04</t>
+          <t>-7,61; 47,0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6,33; 67,14</t>
+          <t>4,07; 67,06</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61,9; 143,79</t>
+          <t>58,69; 134,07</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 48,12</t>
+          <t>-7,66; 46,35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>12,5; 78,93</t>
+          <t>16,05; 78,52</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53,52; 133,51</t>
+          <t>52,66; 127,94</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>11,3</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,73</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,63</t>
+          <t>10,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,4</t>
+          <t>-0,29; 2,29</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,84; 6,77</t>
+          <t>3,75; 6,57</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,99; 11,79</t>
+          <t>9,65; 13,05</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,63</t>
+          <t>-0,35; 2,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,0</t>
+          <t>2,98; 6,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,64</t>
+          <t>7,5; 10,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,17</t>
+          <t>0,08; 2,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,81; 6,0</t>
+          <t>3,73; 5,92</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,28; 10,05</t>
+          <t>8,9; 11,11</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>131,19%</t>
+          <t>154,83%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>102,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>107,32%</t>
+          <t>125,53%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 36,62</t>
+          <t>-3,56; 34,69</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>48,82; 100,89</t>
+          <t>47,45; 98,19</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>80,53; 173,21</t>
+          <t>118,73; 193,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 32,74</t>
+          <t>-3,58; 33,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>30,79; 73,38</t>
+          <t>30,78; 74,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,9; 117,98</t>
+          <t>79,99; 131,62</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,88; 29,01</t>
+          <t>0,68; 29,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>44,39; 80,03</t>
+          <t>43,69; 79,08</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>74,6; 132,38</t>
+          <t>105,75; 149,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Población que conforma un hogar unipersonal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
